--- a/www/download/COUNTRY.SWE.rpA2.xlsx
+++ b/www/download/COUNTRY.SWE.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>7.1209853786912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>6.70421035800362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>7.62718343458456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>7.94723073282277</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>8.26104914409274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>9.13075211422837</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>10.3114045632859</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>9.70685325223753</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>8.06776946061647</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>7.33729552481548</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>7.44934438059463</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>7.36702534389249</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>6.75082699066162</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.51703522574423</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60913399607839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>2.18236186486249</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>2.07425908777328</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>2.50737384515184</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>2.27888097111439</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>2.21879542396331</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>1.98276308426688</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.391</t>
+          <t>1.96018881682427</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>1.77850515609046</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.368</t>
+          <t>1.6569970587485</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>1.51013243884535</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>1.45210120043746</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.423</t>
+          <t>1.48538863126653</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.524</t>
+          <t>1.43639413662685</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>1.65132265708057</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.425</t>
+          <t>1.9776301089934</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>0.710819639399123</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.819</t>
+          <t>0.643077130040694</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>0.860486219469035</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>0.720168607225191</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>0.706889644376488</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>0.54510247240292</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.124</t>
+          <t>0.522847110367251</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>0.450439460110542</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>0.335592104694987</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>0.287186360142945</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>0.254448310319358</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.260213841708357</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>0.223731778186751</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t>0.36281734069701</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>0.515170490233493</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>-0.244947778384968</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>-0.266432988057555</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>-0.165105839221833</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>-0.223359089072564</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>-0.224610446179572</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>-0.301912905431624</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>-0.313156576427259</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>-0.342941021076607</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>-0.449960566827456</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>-0.428110150246393</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>-0.446547455412329</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>-0.448340670437881</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>-0.488182926947546</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>-0.429449665866196</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>-0.353488681075606</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>24054775114.0015</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>23564398464.0508</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>22964072362.3695</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>23919147338.9746</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>24671130529.2489</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>27062004949.9025</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>26118617057.464</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>25886653382.3346</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>26901663505.1958</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>27995523174.3488</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>28808874325.5366</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>29419942225.2154</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>30886832266.8449</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>28701907948.4703</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>24707680877.0162</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>9515747983.38527</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>9896540345.55393</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>8636841378.34141</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>9471130729.53754</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>9845334534.94053</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>11117744799.753</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>11424323403.4135</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>11906722610.2897</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>12819618174.2714</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>13361828762.693</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>13753318695.5332</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>13915920176.7677</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>14909592768.8742</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>13722014662.8459</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>11912724478.9477</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>2255553.87224114</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>2015271.2997744</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>2097138.31735506</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>2185383.27269699</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>2246065.0848717</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>2450974.7732884</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>2525137.13793645</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>2315588.65503324</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>2007293.41717493</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>1791199.77045022</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>1759430.30504615</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>1638162.22551117</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>1464370.51591402</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.12</t>
+          <t>1238915.97300408</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>1277925.91301482</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>48096.9678219437</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>48013.7400552431</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>47036.2540632629</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>47200.8322649097</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>50280.0350607231</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>54230.9635109837</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>53534.7130819243</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>54347.2957329748</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>57794.9305885841</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>63828.612441924</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>68535.0660691982</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>72165.3719618794</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>84061.9160882237</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>93962.2612594818</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>83960.0049298858</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>104930.521106513</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.74</t>
+          <t>102477.520177972</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>98220.4754700023</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>101044.483610719</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>107529.122363379</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>118622.548771048</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>110440.906557909</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>110867.245852027</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>123355.269159887</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>139231.619992638</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>152398.292204725</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>161978.424334427</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>190637.536209238</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>193520.743054291</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>45.84</t>
+          <t>153979.521075511</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>59.57</t>
+          <t>0.880107982711876</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>0.820627636520103</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>1.08328710618119</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.942088576882582</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>0.943147349779187</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>0.845426513114116</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>56.64</t>
+          <t>0.845155141062433</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>0.757514742789056</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>55.97</t>
+          <t>0.62327957762327</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>0.58898405097452</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>53.68</t>
+          <t>0.562551152171232</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>0.592534782115846</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.553590510255475</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.732320285942316</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>47.56</t>
+          <t>0.940397107151962</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>48664.0245698599</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11.54</t>
+          <t>53484.099109837</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>50572.9831406212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>52046.5431885725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>54864.259842949</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>53432.1445377011</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>48358.4082237311</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>52006.600409208</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>62542.9067994847</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>64230.6436042982</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>65520.3671164255</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>67553.0926450966</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>77102.2193546365</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.1209853786912</t>
+          <t>2473.03601626765</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.70421035800362</t>
+          <t>2591.32789022639</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.62718343458456</t>
+          <t>2292.15535518615</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.94723073282277</t>
+          <t>2468.81910422478</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.26104914409274</t>
+          <t>2513.10356721764</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.13075211422837</t>
+          <t>2763.61450688632</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.3114045632859</t>
+          <t>2770.47322810492</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70685325223753</t>
+          <t>2880.05481357482</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.06776946061647</t>
+          <t>3105.82861088074</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7.33729552481548</t>
+          <t>3265.99256029843</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7.44934438059463</t>
+          <t>3351.85189499248</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.36702534389249</t>
+          <t>3336.83104181079</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.75082699066162</t>
+          <t>3493.4259867556</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.51703522574423</t>
+          <t>3175.87767325801</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.60913399607839</t>
+          <t>2817.35350551361</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>12467363982.9384</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>12795880470.7618</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>11377694262.891</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>12236555929.8457</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>12994810867.5913</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>14094895592.8843</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>13384270550.6209</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>14505774974.6529</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>17076950768.0158</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>19673202521.7917</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>19483336804.2399</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>20105302192.0569</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>21036958378.8883</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>19957790424.5907</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>16117477263.8729</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>13157524293.8015</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>13610738160.7585</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>12176026586.5186</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>13388704938.1313</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>14227057249.4944</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>14237717567.6125</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>13510375938.9451</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>14449148910.0114</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>16579941654.1409</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>18557035010.1743</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>17900749526.8558</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>17971728656.1177</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>18497048632.854</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>17433609871.2583</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>13707444066.3485</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-690160310.863084</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-814857689.996684</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-798332323.627638</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-1152149008.28561</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1232246381.90311</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-142821974.728168</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-126105388.32413</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>56626064.6415689</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>497009113.87492</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1116167511.61733</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>1582587277.38406</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>2133573535.93918</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>2539909746.03426</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2524180553.3324</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2410033197.52437</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>4649.57475571878</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>4717.8431722315</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>4775.21769682347</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>4794.66538070444</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>4883.33053635958</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>5100.0474830348</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>5111.95292001363</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>5061.73879489833</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>5041.62815564076</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>5189.61008891565</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>5237.44004042783</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>5314.01949612754</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>5427.35346130336</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>5501.63731905613</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>5466.78459192305</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>4643.81716374309</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>4709.50485533641</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>4771.45083452181</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>4798.32100657843</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>4886.34202560762</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>5093.2051326546</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>5105.57684126624</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>5059.39658066974</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>5057.04467516508</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>5200.92400165816</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>5266.03590642228</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>5334.34392226926</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>5444.17750478658</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>5521.61836770858</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>5504.44839726116</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>218.24</t>
+          <t>96725.5237641605</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>207.43</t>
+          <t>102366.696057867</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>250.74</t>
+          <t>101699.771226788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>227.89</t>
+          <t>104969.377987809</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>221.88</t>
+          <t>107075.320954573</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>198.28</t>
+          <t>110832.788765628</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>196.02</t>
+          <t>100696.185240731</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>177.85</t>
+          <t>106311.677138873</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>165.7</t>
+          <t>130882.297248063</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>151.01</t>
+          <t>159190.879264687</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>145.21</t>
+          <t>170943.424743657</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>148.54</t>
+          <t>192960.40986097</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>143.64</t>
+          <t>226789.430813134</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>165.13</t>
+          <t>248132.595279107</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>197.76</t>
+          <t>181913.166040362</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>6384201395.62186</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>64.31</t>
+          <t>6219240899.10829</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>6327563208.75438</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>6639833938.95772</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>6909700469.13009</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>54.51</t>
+          <t>7710425130.74042</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>7141565178.60939</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>6986304713.43842</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>7502370528.9754</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>8250869329.72399</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>8572088650.69615</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>9076990648.40855</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>9464490994.73825</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>8968953316.78362</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>7023550478.09656</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-24.49</t>
+          <t>75831.3495973377</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-26.64</t>
+          <t>79890.6155496373</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>78082.0581520606</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>83083.1034853668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-22.46</t>
+          <t>85453.4305373733</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>89747.980114205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-31.32</t>
+          <t>81785.0223451439</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-34.29</t>
+          <t>85720.0656918854</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>104826.942952039</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-42.81</t>
+          <t>123953.538242074</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-44.65</t>
+          <t>136436.242345256</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-44.83</t>
+          <t>155369.566848147</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>186026.553897001</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-42.94</t>
+          <t>208723.923020259</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-35.35</t>
+          <t>152138.611332661</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19173.857</t>
+          <t>12842872284.4354</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19289.19</t>
+          <t>12689018134.7792</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19291.93</t>
+          <t>11522482642.9803</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19727.817</t>
+          <t>12778787306.1701</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20511.398</t>
+          <t>13648647786.1729</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>21904.347</t>
+          <t>15572121348.783</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22419.609</t>
+          <t>14603025769.1091</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>22227.447</t>
+          <t>15054294970.4919</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22088.665</t>
+          <t>16864525363.4657</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>22558.488</t>
+          <t>18250474474.7775</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>22901.464</t>
+          <t>19232557706.3733</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>23591.136</t>
+          <t>20349137922.7853</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>24631.092</t>
+          <t>21997623728.7676</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>25077.237</t>
+          <t>21490980306.6195</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>24356.421</t>
+          <t>16876110123.9458</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17890.634</t>
+          <t>20894.1741668229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18017.915</t>
+          <t>22476.0805082296</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17993.02</t>
+          <t>23617.7130747272</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18393.775</t>
+          <t>21886.274502442</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19130.936</t>
+          <t>21621.8904171997</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20516.981</t>
+          <t>21084.8086514232</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21079.649</t>
+          <t>18911.1628955872</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>20926.241</t>
+          <t>20591.611446988</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20809.824</t>
+          <t>26055.3542960244</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>21231.733</t>
+          <t>35237.341022613</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21490.264</t>
+          <t>34507.182398401</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>22161.587</t>
+          <t>37590.8430128234</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23163.402</t>
+          <t>40762.8769161332</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>23770.924</t>
+          <t>39408.6722588476</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>23115.416</t>
+          <t>29774.5547077013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>24054.775</t>
+          <t>-6458670888.8135</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>23564.398</t>
+          <t>-6469777235.67095</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22964.072</t>
+          <t>-5194919434.22595</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23919.147</t>
+          <t>-6138953367.21237</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>24671.131</t>
+          <t>-6738947317.04285</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>27062.005</t>
+          <t>-7861696218.04254</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>26118.617</t>
+          <t>-7461460590.49971</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>25886.653</t>
+          <t>-8067990257.05351</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26901.664</t>
+          <t>-9362154834.49033</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>27995.523</t>
+          <t>-9999605145.05356</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>28808.874</t>
+          <t>-10660469055.6771</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>29419.942</t>
+          <t>-11272147274.3767</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>30886.832</t>
+          <t>-12533132734.0293</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>28701.908</t>
+          <t>-12522026989.8359</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>24707.681</t>
+          <t>-9852559645.84921</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>114854.61053</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>122774.93584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>112054.99439</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>112549.77093</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>113330.15737</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>108058.67783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>99019.68258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110070.99521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>138070.00793</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>158839.5881</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>160076.10059</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>172003.34448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>199903.80459</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>208735.56022</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>167415.59572</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11025.979</t>
+          <t>0.0535880004430437</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11040.616</t>
+          <t>0.0446475249065349</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10997.136</t>
+          <t>0.0447102742219196</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11173.333</t>
+          <t>0.0425321401521922</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11536.087</t>
+          <t>0.044700616629324</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12372.004</t>
+          <t>0.0349235375180972</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12660.641</t>
+          <t>0.0276544014955168</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>12689.678</t>
+          <t>0.0323535428974781</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>12604.081</t>
+          <t>0.0403038827323497</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12834.121</t>
+          <t>0.0547857361478185</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12955.645</t>
+          <t>0.054832707452759</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>13107.308</t>
+          <t>0.0666301044100791</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>13619.596</t>
+          <t>0.0647866830108882</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>13935.954</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>13472.292</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>133127.784362746</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>150511.0878089</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>136807.643597456</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>137032.009325101</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>136351.930258648</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>135897.23871761</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>128638.440508168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>140953.50530439</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>174679.259001201</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>198006.744264434</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>201662.713361205</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>211588.521117675</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>248571.027188134</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>262905.781776772</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>222136.709758279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9515.748</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9896.54</t>
+          <t>161542.668371692</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8636.841</t>
+          <t>147085.249329839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9471.131</t>
+          <t>147365.163379276</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9845.335</t>
+          <t>146513.806072053</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11117.745</t>
+          <t>145381.994219881</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11424.323</t>
+          <t>136976.405454252</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11906.723</t>
+          <t>149877.465676238</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12819.618</t>
+          <t>185578.561508121</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>13361.829</t>
+          <t>210743.792381888</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13753.319</t>
+          <t>215298.41297581</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>13915.92</t>
+          <t>225476.100933943</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>14909.593</t>
+          <t>264880.656011057</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>13722.015</t>
+          <t>280324.241073704</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11912.724</t>
+          <t>237231.086161039</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>545298.549566519</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>82.06</t>
+          <t>595671.882688816</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>546296.317448332</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>94.21</t>
+          <t>550559.584078313</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>94.31</t>
+          <t>559827.924355327</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>546059.288310521</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>84.52</t>
+          <t>516590.591712231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>75.75</t>
+          <t>572674.271663728</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>700425.904121031</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>789646.203294406</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>808590.697184944</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>59.25</t>
+          <t>855373.532513009</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>55.36</t>
+          <t>985730.606451543</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>149845.764626259</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>153009.12433474</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.185</t>
+          <t>158833.376482047</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.246</t>
+          <t>162872.121386245</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>178176.232055176</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.525</t>
+          <t>190976.721517479</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.316</t>
+          <t>196148.574637276</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.007</t>
+          <t>198444.141333506</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>204866.178068768</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>215662.279492884</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>220237.056421005</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>233223.897723086</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>236013.372408089</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>228839.713418951</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>133127.784362746</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>139368.926890817</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>142042.186841521</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>147728.752951229</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>151644.686131021</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>166730.278943514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>179849.433456003</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>185100.922674331</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>187522.568122355</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>193222.90210259</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>201851.287700017</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>207426.50935102</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>220500.176045215</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>223347.6713283</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>215879.258804695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>77885.4834856216</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80079.3743283085</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>74998.0413001609</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75463.020580724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79888.9132679466</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>72502.466580119</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62644.4118557478</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>70534.6420237624</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90772.7903018787</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107491.992148112</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109857.58426419</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>124546.720426057</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140964.435688943</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>150830.402136296</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>116473.816238961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>17890633745.0371</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>18017914859.0517</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>17993020281.6308</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>18393774799.9964</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>19130935709.2592</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>20516981019.5007</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>21079649060.9682</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20926240525.884</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>20809824375.2228</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>21231732795.7717</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>21490263973.8835</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>22161586906.6503</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>23163401837.4966</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>23770924364.4458</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>23115416117.2485</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19173856687.3595</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19289189986.4676</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19291930014.1386</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>19727816986.4466</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20511397920.9232</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>21904347314.0347</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>22419609025.3683</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>22227446997.8828</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>22088665436.6535</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>22558487764.7921</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>22901463553.4399</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>23591135996.2358</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>24631092284.9059</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>25077237427.3797</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>24356420588.1456</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>11025979213.882</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11040615546.1821</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10997136155.1131</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>11173332982.8887</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11536086975.6413</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12372003621.3757</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12660641005.6478</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>12689677605.8141</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>12604080762.7359</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12834120574.7581</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12955644559.5042</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13107307855.991</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>13619596402.0266</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>13935954000.255</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>13472291599.2382</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4128899.99999584</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4095799.9999959</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4043200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4111400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4197700.00000615</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4300700.00000532</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4391200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4393300.00000522</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4367900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4337400</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4348900</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4422500</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4524300</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4541646.26335567</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4424861.28133468</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3847799.99999621</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3819099.99999627</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3768000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3836300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3917600.00000346</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4022900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4123600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4134200.00000303</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4127600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4091200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4103200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4170400</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4267900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4320700</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4228338.56512301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.175632394391622</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.178519764421943</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.182521612994752</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.185480918571493</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199769360570896</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.218077092896323</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.225195429041695</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.231065372362702</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.22077703781729</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.238035604533249</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.249053314488781</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.25943802992654</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.262575913097484</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.27981093651643</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292918479894697</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.568263560293997</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.574674634470877</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.580260119671008</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.586000513061219</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.574163857675759</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.582930939050782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.583532617697635</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.584072145887833</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.583415741425941</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.585317212081492</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.581267224553589</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.574570886085595</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.570379798923343</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.561167767493832</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.530134638009854</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.256104045314381</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.24680560110718</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.23721826733424</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.228518568367287</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.226066781753345</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.198991968052896</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.19127195326067</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.184862481749466</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.195807220756769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.176647183385259</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.16967946095763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.165991083987865</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.167044287979174</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.159021295989738</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.176946882095448</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.28483906005986</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.287373374823972</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.293555082319156</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.298545897251331</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.313840724744835</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.340168230617697</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.350500995584561</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.359416621111238</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.363874227389124</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.375984919931042</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.394208050438851</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.411549684612957</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.417460150610919</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.436912596125648</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.458407403898322</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.595686295761917</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.597197672815913</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.59651254627171</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.596031432577136</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.582581363577168</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.571963368879507</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.566430318150786</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.560450042836751</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.559692976091991</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.550289334495076</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.53682564494479</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.522531436565446</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.518849539404371</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.503813541998521</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.475587232730029</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.119474644178223</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.115428952360115</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.109932371409133</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.105422670171533</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.103577911677997</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.087868400502796</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0830686862646533</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0801333360520105</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0764327965188853</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0737257455738823</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0689663046163588</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0659188788215971</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0636903099847101</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0592738618758306</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0660053633716489</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461976.65331</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>501511.41338</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>466168.81334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>468861.31007</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>476120.03486</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>466126.22559</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>430428.36138</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>466075.03516</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>573860.72027</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>666076.61884</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>694302.57719</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>753739.90604</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>880097.95041</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>949568.28984</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>757060.99647</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>221026.57373</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>241622.0427</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>222083.29063</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>222828.18396</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226402.71934</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>217884.4608</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>199620.81731</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>220412.1077</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>276351.35181</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>318235.78453</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>325155.99724</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>350022.82136</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>405845.0917</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>431154.64321</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>353704.9024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3883063.05764445</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4018765.57132922</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4144897.71115209</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4291173.96676717</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4451909.0550342</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4621620.99180891</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4765026.77031318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4883940.32262649</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5000945.27065932</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5138989.3150617</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5306922.67425119</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5502674.76391365</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5725293.18762794</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
